--- a/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
+++ b/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
@@ -856,7 +856,7 @@
     <t xml:space="preserve">クルイツゥアは危険な存在だ。汝も知っているだろう。娘の災眼は、一つの村に死をもたらした。そして、その力はまだ「目覚めてすら」いないのだ。</t>
   </si>
   <si>
-    <t xml:space="preserve">Quruitzia is a dangerous being. Thou knowest it well. The girl's Ill-Eye brought death to an entire village. And that power hath not even 'awakened' yet.</t>
+    <t xml:space="preserve">Quruitzia is a dangerous being. Thou knowest it well. The girl's Ill Eye brought death to an entire village. And that power hath not even 'awakened' yet.</t>
   </si>
   <si>
     <t xml:space="preserve">だが、その引き金を引いたのは何だ？クルイツゥアを追い詰めたのは、迷信深い村人達だろう？
@@ -1114,7 +1114,7 @@
   </si>
   <si>
     <t xml:space="preserve">How ironic. Whether I remember this old face or not, I never possessed the humanity you hoped for in the first place.
-...No matter. I’ve no wish to sour a reunion two centuries in the making. Let us talk here, as we once did in this dusky room... of the very crystal we call the Magic Stone.”</t>
+...No matter. I’ve no wish to sour a reunion two centuries in the making. Let us talk here, as we once did in this dusky room... of the very crystal we call the "Magic Stone.”</t>
   </si>
   <si>
     <t xml:space="preserve">どうやら、私が君に会いに来ることも、その理由も、君にはお見通しだったみたいだね。</t>
